--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:39:42+00:00</t>
+    <t>2026-07-23T11:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:20:28+00:00</t>
+    <t>2026-07-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:55:45+00:00</t>
+    <t>2026-07-24T06:29:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$8</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="118">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T06:29:13+00:00</t>
+    <t>2026-09-03T10:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,178 +78,178 @@
     <t>Jurisdiction</t>
   </si>
   <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Priorität der (einzelnen) Empfehlung</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>complex-type</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Derivation</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>Context</t>
+  </si>
+  <si>
+    <t>element:MedicationRequest</t>
+  </si>
+  <si>
+    <t>element:RequestGroup</t>
+  </si>
+  <si>
+    <t>element:ServiceRequest</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Slice Name</t>
+  </si>
+  <si>
+    <t>Alias(s)</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Must Support?</t>
+  </si>
+  <si>
+    <t>Is Modifier?</t>
+  </si>
+  <si>
+    <t>Is Summary?</t>
+  </si>
+  <si>
+    <t>Type(s)</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>Default Value</t>
+  </si>
+  <si>
+    <t>Meaning When Missing</t>
+  </si>
+  <si>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Minimum Value</t>
+  </si>
+  <si>
+    <t>Maximum Value</t>
+  </si>
+  <si>
+    <t>Maximum Length</t>
+  </si>
+  <si>
+    <t>Binding Strength</t>
+  </si>
+  <si>
+    <t>Binding Description</t>
+  </si>
+  <si>
+    <t>Binding Value Set</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Slicing Discriminator</t>
+  </si>
+  <si>
+    <t>Slicing Description</t>
+  </si>
+  <si>
+    <t>Slicing Ordered</t>
+  </si>
+  <si>
+    <t>Slicing Rules</t>
+  </si>
+  <si>
+    <t>Base Path</t>
+  </si>
+  <si>
+    <t>Base Min</t>
+  </si>
+  <si>
+    <t>Base Max</t>
+  </si>
+  <si>
+    <t>Condition(s)</t>
+  </si>
+  <si>
+    <t>Constraint(s)</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Priorität der (einzelnen) Empfehlung</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>complex-type</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Derivation</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>Context</t>
-  </si>
-  <si>
-    <t>element:MedicationRequest</t>
-  </si>
-  <si>
-    <t>element:RequestGroup</t>
-  </si>
-  <si>
-    <t>element:ServiceRequest</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Slice Name</t>
-  </si>
-  <si>
-    <t>Alias(s)</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Must Support?</t>
-  </si>
-  <si>
-    <t>Is Modifier?</t>
-  </si>
-  <si>
-    <t>Is Summary?</t>
-  </si>
-  <si>
-    <t>Type(s)</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Requirements</t>
-  </si>
-  <si>
-    <t>Default Value</t>
-  </si>
-  <si>
-    <t>Meaning When Missing</t>
-  </si>
-  <si>
-    <t>Fixed Value</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Minimum Value</t>
-  </si>
-  <si>
-    <t>Maximum Value</t>
-  </si>
-  <si>
-    <t>Maximum Length</t>
-  </si>
-  <si>
-    <t>Binding Strength</t>
-  </si>
-  <si>
-    <t>Binding Description</t>
-  </si>
-  <si>
-    <t>Binding Value Set</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Slicing Discriminator</t>
-  </si>
-  <si>
-    <t>Slicing Description</t>
-  </si>
-  <si>
-    <t>Slicing Ordered</t>
-  </si>
-  <si>
-    <t>Slicing Rules</t>
-  </si>
-  <si>
-    <t>Base Path</t>
-  </si>
-  <si>
-    <t>Base Min</t>
-  </si>
-  <si>
-    <t>Base Max</t>
-  </si>
-  <si>
-    <t>Condition(s)</t>
-  </si>
-  <si>
-    <t>Constraint(s)</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t>0</t>
@@ -289,9 +289,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Extension.extension</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
   </si>
   <si>
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -728,7 +722,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK8"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="28.57421875" customWidth="true" bestFit="true"/>
@@ -766,7 +760,6 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,9 +871,6 @@
       <c r="AJ1" t="s" s="1">
         <v>76</v>
       </c>
-      <c r="AK1" t="s" s="1">
-        <v>77</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -891,7 +881,7 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
@@ -901,13 +891,13 @@
         <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="K2" t="s" s="2">
         <v>80</v>
@@ -921,50 +911,50 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
@@ -980,9 +970,6 @@
       </c>
       <c r="AJ2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
@@ -994,7 +981,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
@@ -1004,13 +991,13 @@
         <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="K3" t="s" s="2">
         <v>85</v>
@@ -1024,50 +1011,50 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>88</v>
@@ -1079,25 +1066,22 @@
         <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK3" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1107,73 +1091,73 @@
         <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1182,25 +1166,22 @@
         <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AK4" t="s" s="2">
-        <v>20</v>
-      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -1210,75 +1191,75 @@
         <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>100</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
         <v>3</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>84</v>
@@ -1287,25 +1268,22 @@
         <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1315,73 +1293,73 @@
         <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="I6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AC6" s="2"/>
       <c r="AD6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1390,27 +1368,24 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1420,73 +1395,73 @@
         <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1495,27 +1470,24 @@
         <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1525,73 +1497,73 @@
         <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -1600,17 +1572,14 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK8">
+  <autoFilter ref="A1:AJ8">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:43:48+00:00</t>
+    <t>2026-09-03T17:01:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T17:01:55+00:00</t>
+    <t>2026-09-04T05:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T05:29:06+00:00</t>
+    <t>2026-09-04T06:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T06:37:14+00:00</t>
+    <t>2026-09-04T07:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T07:02:52+00:00</t>
+    <t>2026-09-04T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T08:01:15+00:00</t>
+    <t>2026-09-04T11:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:35:42+00:00</t>
+    <t>2026-09-04T11:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:20+00:00</t>
+    <t>2026-09-04T12:44:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:44:12+00:00</t>
+    <t>2026-09-04T13:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:01:37+00:00</t>
+    <t>2026-09-04T16:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:11:50+00:00</t>
+    <t>2026-09-04T16:57:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:57:12+00:00</t>
+    <t>2026-09-07T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:50:41+00:00</t>
+    <t>2026-09-07T16:06:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T16:06:13+00:00</t>
+    <t>2026-09-08T09:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:37+00:00</t>
+    <t>2026-09-08T09:32:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:32:56+00:00</t>
+    <t>2026-09-08T15:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:03:47+00:00</t>
+    <t>2026-09-09T09:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:29:55+00:00</t>
+    <t>2026-09-09T10:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:02:49+00:00</t>
+    <t>2026-09-09T11:08:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:08:17+00:00</t>
+    <t>2026-09-09T11:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:49:20+00:00</t>
+    <t>2026-09-11T10:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:52:45+00:00</t>
+    <t>2026-09-11T12:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-seltene-empfehlung-prioritaet.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="118">
   <si>
     <t>Property</t>
   </si>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:45:52+00:00</t>
+    <t>2026-09-11T14:10:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -589,98 +589,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -874,10 +876,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -906,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -957,7 +959,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>
@@ -1103,7 +1105,7 @@
         <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
         <v>91</v>
